--- a/survey_templates/035_performance_appraisal_form--survey_templates.xlsx
+++ b/survey_templates/035_performance_appraisal_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>performance_appraisal_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance Appraisal Form</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,73 +538,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>current_job_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your current job title?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your current job title</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>self_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Briefly describe the employees performance</t>
-        </is>
-      </c>
+          <t>How do you rate your performance in this role?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>quarterly_accomplishments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>List your major accomplishments in the past quarter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,141 +616,187 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>quarterly_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Survey Templates, Employment Forms</t>
+          <t>What are your top 3 goals for the next quarter?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>goal_strategy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>How do you plan to achieve these goals?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Select assigned tool</t>
+          <t>Provide a clear plan of action</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>used_tools</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter the output file name</t>
-        </is>
-      </c>
+          <t>What tools do you use for this role?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tools</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Which tools have been assigned to you?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>manager_feedback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What feedback do you have for your manager?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>role_improvement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What areas for improvement do you suggest for your role?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>output_format</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the expected output format for the appraisal?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>output_file_name</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What is the name of the output file?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide the name of the output file</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -765,10 +811,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -793,238 +839,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_templates</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Templates</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employment_forms</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Employment Forms</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quarterly_accomplishments_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>accomplishment_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Accomplishment 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quarterly_accomplishments_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>accomplishment_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Accomplishment 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quarterly_accomplishments_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>accomplishment_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Accomplishment 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quarterly_goals_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quarterly_goals_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quarterly_goals_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>used_tools_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>used_tools_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>used_tools_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tools_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>assigned_tools_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>tool_2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tool 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>assigned_tools_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tool_3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tool 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>role_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>area_1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Area 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>role_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>area_2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Area 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>role_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>area_3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Area 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>output_format_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>format_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Format 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>output_format_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>format_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Format 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>output_format_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>format_3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Format 3</t>
         </is>
       </c>
     </row>
